--- a/artfynd/A 28663-2023 artfynd.xlsx
+++ b/artfynd/A 28663-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 28663-2023 artfynd.xlsx
+++ b/artfynd/A 28663-2023 artfynd.xlsx
@@ -2524,11 +2524,11 @@
         <v>110955882</v>
       </c>
       <c r="B18" t="n">
-        <v>89845</v>
+        <v>91168</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2562,10 +2562,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>570722.805741926</v>
+        <v>570723</v>
       </c>
       <c r="R18" t="n">
-        <v>7054827.94732958</v>
+        <v>7054828</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>

--- a/artfynd/A 28663-2023 artfynd.xlsx
+++ b/artfynd/A 28663-2023 artfynd.xlsx
@@ -2524,7 +2524,7 @@
         <v>110955882</v>
       </c>
       <c r="B18" t="n">
-        <v>91168</v>
+        <v>91182</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 28663-2023 artfynd.xlsx
+++ b/artfynd/A 28663-2023 artfynd.xlsx
@@ -2524,7 +2524,7 @@
         <v>110955882</v>
       </c>
       <c r="B18" t="n">
-        <v>91182</v>
+        <v>91184</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 28663-2023 artfynd.xlsx
+++ b/artfynd/A 28663-2023 artfynd.xlsx
@@ -2524,7 +2524,7 @@
         <v>110955882</v>
       </c>
       <c r="B18" t="n">
-        <v>91184</v>
+        <v>91185</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 28663-2023 artfynd.xlsx
+++ b/artfynd/A 28663-2023 artfynd.xlsx
@@ -2524,7 +2524,7 @@
         <v>110955882</v>
       </c>
       <c r="B18" t="n">
-        <v>91185</v>
+        <v>91194</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 28663-2023 artfynd.xlsx
+++ b/artfynd/A 28663-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AY68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110490872</v>
+        <v>110490783</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570672.9618235506</v>
+        <v>570646</v>
       </c>
       <c r="R2" t="n">
-        <v>7054685.3300488</v>
+        <v>7054656</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,19 +744,9 @@
           <t>2023-06-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-06-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,37 +773,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110491011</v>
+        <v>110954705</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +809,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570655.8098812394</v>
+        <v>570865</v>
       </c>
       <c r="R3" t="n">
-        <v>7054695.182702375</v>
+        <v>7054482</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -859,22 +839,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-07-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>17:04</t>
+          <t>2023-07-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-07-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>17:04</t>
+          <t>2023-07-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,15 +871,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110490866</v>
+        <v>110956010</v>
       </c>
       <c r="B4" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,21 +882,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +907,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570672.9618235506</v>
+        <v>570701</v>
       </c>
       <c r="R4" t="n">
-        <v>7054685.3300488</v>
+        <v>7054822</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -972,22 +937,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-06-30</t>
+          <t>2023-07-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-06-30</t>
+          <t>2023-07-20</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,15 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110490772</v>
+        <v>110956165</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1030,21 +990,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1015,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570645.9931480226</v>
+        <v>570668</v>
       </c>
       <c r="R5" t="n">
-        <v>7054655.804135857</v>
+        <v>7054855</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1085,22 +1045,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-06-30</t>
+          <t>2023-07-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-06-30</t>
+          <t>2023-07-20</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,15 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110490783</v>
+        <v>110490772</v>
       </c>
       <c r="B6" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,21 +1098,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570645.9931480226</v>
+        <v>570646</v>
       </c>
       <c r="R6" t="n">
-        <v>7054655.804135857</v>
+        <v>7054656</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1201,19 +1156,9 @@
           <t>2023-06-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-06-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,12 +1188,7 @@
         <v>110542947</v>
       </c>
       <c r="B7" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1283,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570495.6265576768</v>
+        <v>570496</v>
       </c>
       <c r="R7" t="n">
-        <v>7054704.967067718</v>
+        <v>7054705</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1316,19 +1256,9 @@
           <t>2023-07-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-07-01</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,51 +1286,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110956446</v>
+        <v>110542948</v>
       </c>
       <c r="B8" t="n">
-        <v>6202</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105336</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kulltjärnen, Ång</t>
+          <t>Kulltjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>570628.0134740177</v>
+        <v>570538</v>
       </c>
       <c r="R8" t="n">
-        <v>7054922.837781735</v>
+        <v>7054666</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1427,22 +1354,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>21:19</t>
+          <t>2023-07-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>21:19</t>
+          <t>2023-07-01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1451,33 +1368,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110955691</v>
+        <v>110956330</v>
       </c>
       <c r="B9" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1485,21 +1398,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1510,10 +1423,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>570848.2683770747</v>
+        <v>570668</v>
       </c>
       <c r="R9" t="n">
-        <v>7054796.484926676</v>
+        <v>7054855</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1545,7 +1458,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1555,12 +1468,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,37 +1495,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110955973</v>
+        <v>110957421</v>
       </c>
       <c r="B10" t="n">
-        <v>89845</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1628,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>570718.1747571867</v>
+        <v>570780</v>
       </c>
       <c r="R10" t="n">
-        <v>7054815.8296258</v>
+        <v>7054421</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1663,7 +1566,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>21:19</t>
+          <t>22:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1673,7 +1576,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>21:19</t>
+          <t>22:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1700,15 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110956757</v>
+        <v>110955882</v>
       </c>
       <c r="B11" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1716,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1741,10 +1639,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>570567.5278309077</v>
+        <v>570723</v>
       </c>
       <c r="R11" t="n">
-        <v>7054797.788776807</v>
+        <v>7054828</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1787,11 +1685,6 @@
       <c r="AB11" t="inlineStr">
         <is>
           <t>21:19</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,15 +1711,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110955216</v>
+        <v>110955973</v>
       </c>
       <c r="B12" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1834,21 +1722,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1859,10 +1747,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>570765.4646628352</v>
+        <v>570718</v>
       </c>
       <c r="R12" t="n">
-        <v>7054613.522815875</v>
+        <v>7054816</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1894,7 +1782,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1904,12 +1792,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1936,15 +1819,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110954677</v>
+        <v>110956252</v>
       </c>
       <c r="B13" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,21 +1830,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1977,10 +1855,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>570819.0374729836</v>
+        <v>570654</v>
       </c>
       <c r="R13" t="n">
-        <v>7054509.250309445</v>
+        <v>7054866</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2012,7 +1890,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2022,12 +1900,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2054,37 +1927,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>110957165</v>
+        <v>110955652</v>
       </c>
       <c r="B14" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2095,10 +1963,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>570689.5347253014</v>
+        <v>570851</v>
       </c>
       <c r="R14" t="n">
-        <v>7054561.54293094</v>
+        <v>7054767</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2128,24 +1996,9 @@
           <t>2023-07-20</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>22:19</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-07-20</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>22:19</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>60-tal plantor</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2172,37 +2025,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>110956564</v>
+        <v>110954865</v>
       </c>
       <c r="B15" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2213,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>570572.2677499688</v>
+        <v>570847</v>
       </c>
       <c r="R15" t="n">
-        <v>7054885.109238528</v>
+        <v>7054529</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2246,24 +2094,9 @@
           <t>2023-07-20</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>21:19</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-07-20</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>21:19</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2293,12 +2126,7 @@
         <v>110956168</v>
       </c>
       <c r="B16" t="n">
-        <v>89369</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2331,10 +2159,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>570667.8388443358</v>
+        <v>570668</v>
       </c>
       <c r="R16" t="n">
-        <v>7054855.200111266</v>
+        <v>7054855</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2403,19 +2231,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>110956381</v>
+        <v>110490872</v>
       </c>
       <c r="B17" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2444,10 +2267,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>570686.076392094</v>
+        <v>570673</v>
       </c>
       <c r="R17" t="n">
-        <v>7054896.543924876</v>
+        <v>7054685</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2474,27 +2297,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>21:19</t>
+          <t>2023-06-30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>21:19</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2023-06-30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2521,15 +2329,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>110955882</v>
+        <v>110954395</v>
       </c>
       <c r="B18" t="n">
-        <v>91194</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2537,21 +2340,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2562,10 +2365,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>570723</v>
+        <v>570797</v>
       </c>
       <c r="R18" t="n">
-        <v>7054828</v>
+        <v>7054342</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2595,19 +2398,14 @@
           <t>2023-07-20</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>21:19</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-07-20</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>21:19</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2634,19 +2432,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>110957358</v>
+        <v>110954434</v>
       </c>
       <c r="B19" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2675,10 +2468,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>570784.736545446</v>
+        <v>570810</v>
       </c>
       <c r="R19" t="n">
-        <v>7054448.85087682</v>
+        <v>7054374</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2708,19 +2501,9 @@
           <t>2023-07-20</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>22:19</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-07-20</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>22:19</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2752,19 +2535,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>110956508</v>
+        <v>110954677</v>
       </c>
       <c r="B20" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2793,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>570597.6128096103</v>
+        <v>570819</v>
       </c>
       <c r="R20" t="n">
-        <v>7054867.42974645</v>
+        <v>7054509</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2826,19 +2604,9 @@
           <t>2023-07-20</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>21:19</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-07-20</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>21:19</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2870,37 +2638,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>110954865</v>
+        <v>110954981</v>
       </c>
       <c r="B21" t="n">
-        <v>89369</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2911,10 +2674,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>570846.6798232374</v>
+        <v>570839</v>
       </c>
       <c r="R21" t="n">
-        <v>7054528.558678756</v>
+        <v>7054561</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2944,19 +2707,14 @@
           <t>2023-07-20</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-07-20</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2983,19 +2741,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>110954981</v>
+        <v>110955090</v>
       </c>
       <c r="B22" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -3024,10 +2777,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>570839.2636377254</v>
+        <v>570795</v>
       </c>
       <c r="R22" t="n">
-        <v>7054561.324296553</v>
+        <v>7054577</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3057,24 +2810,14 @@
           <t>2023-07-20</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-07-20</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Rikligt, även på tallstammar</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3101,37 +2844,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>110957421</v>
+        <v>110955216</v>
       </c>
       <c r="B23" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3142,10 +2880,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>570780.0172228366</v>
+        <v>570765</v>
       </c>
       <c r="R23" t="n">
-        <v>7054420.708478829</v>
+        <v>7054614</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3175,19 +2913,14 @@
           <t>2023-07-20</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>22:19</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-07-20</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>22:19</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3214,19 +2947,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>110956836</v>
+        <v>110955319</v>
       </c>
       <c r="B24" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3255,10 +2983,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>570591.8645085217</v>
+        <v>570716</v>
       </c>
       <c r="R24" t="n">
-        <v>7054745.37741222</v>
+        <v>7054627</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3288,19 +3016,9 @@
           <t>2023-07-20</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>21:19</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-07-20</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>21:19</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3332,19 +3050,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>110955319</v>
+        <v>110955501</v>
       </c>
       <c r="B25" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3373,10 +3086,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>570716.5910909711</v>
+        <v>570663</v>
       </c>
       <c r="R25" t="n">
-        <v>7054627.117655913</v>
+        <v>7054687</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3406,19 +3119,9 @@
           <t>2023-07-20</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-07-20</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3450,37 +3153,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>110956010</v>
+        <v>110955580</v>
       </c>
       <c r="B26" t="n">
-        <v>89686</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3491,10 +3189,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>570701.1126214273</v>
+        <v>570726</v>
       </c>
       <c r="R26" t="n">
-        <v>7054821.678806251</v>
+        <v>7054723</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3524,19 +3222,14 @@
           <t>2023-07-20</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>21:19</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-07-20</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>21:19</t>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3563,19 +3256,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>110956103</v>
+        <v>110955614</v>
       </c>
       <c r="B27" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3604,10 +3292,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>570678.9038570094</v>
+        <v>570773</v>
       </c>
       <c r="R27" t="n">
-        <v>7054838.537736276</v>
+        <v>7054769</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3637,24 +3325,14 @@
           <t>2023-07-20</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>21:19</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2023-07-20</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>21:19</t>
-        </is>
-      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3681,15 +3359,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>110957182</v>
+        <v>110955639</v>
       </c>
       <c r="B28" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3697,21 +3370,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3722,10 +3395,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>570715.3968322413</v>
+        <v>570841</v>
       </c>
       <c r="R28" t="n">
-        <v>7054560.784544432</v>
+        <v>7054791</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3755,24 +3428,9 @@
           <t>2023-07-20</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>22:19</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-07-20</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>22:19</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>60-tal plantor</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3799,19 +3457,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>110955090</v>
+        <v>110955691</v>
       </c>
       <c r="B29" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3840,10 +3493,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>570795.248416111</v>
+        <v>570849</v>
       </c>
       <c r="R29" t="n">
-        <v>7054576.806798867</v>
+        <v>7054796</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3873,24 +3526,14 @@
           <t>2023-07-20</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-07-20</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Rikligt, även på tallstammar</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3917,37 +3560,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>110955274</v>
+        <v>110955719</v>
       </c>
       <c r="B30" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3958,10 +3596,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>570757.4465870578</v>
+        <v>570877</v>
       </c>
       <c r="R30" t="n">
-        <v>7054633.369155373</v>
+        <v>7054841</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3991,19 +3629,14 @@
           <t>2023-07-20</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-07-20</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4030,19 +3663,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>110955501</v>
+        <v>110955757</v>
       </c>
       <c r="B31" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -4071,10 +3699,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>570662.6687993431</v>
+        <v>570755</v>
       </c>
       <c r="R31" t="n">
-        <v>7054687.325626028</v>
+        <v>7054858</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4104,19 +3732,9 @@
           <t>2023-07-20</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-07-20</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4148,37 +3766,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>110955652</v>
+        <v>110955822</v>
       </c>
       <c r="B32" t="n">
-        <v>90666</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4189,10 +3802,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>570850.7156756282</v>
+        <v>570735</v>
       </c>
       <c r="R32" t="n">
-        <v>7054766.725643804</v>
+        <v>7054864</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4224,7 +3837,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4234,7 +3847,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4261,19 +3879,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>110955580</v>
+        <v>110955922</v>
       </c>
       <c r="B33" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -4302,10 +3915,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>570725.147074289</v>
+        <v>570710</v>
       </c>
       <c r="R33" t="n">
-        <v>7054722.983191215</v>
+        <v>7054807</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4337,7 +3950,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4347,7 +3960,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4379,37 +3992,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>110956165</v>
+        <v>110956103</v>
       </c>
       <c r="B34" t="n">
-        <v>89686</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4420,10 +4028,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>570667.8388443358</v>
+        <v>570679</v>
       </c>
       <c r="R34" t="n">
-        <v>7054855.200111266</v>
+        <v>7054839</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4466,6 +4074,11 @@
       <c r="AB34" t="inlineStr">
         <is>
           <t>21:19</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4495,16 +4108,11 @@
         <v>110956348</v>
       </c>
       <c r="B35" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4533,10 +4141,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>570673.182192896</v>
+        <v>570673</v>
       </c>
       <c r="R35" t="n">
-        <v>7054875.342939081</v>
+        <v>7054875</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4610,15 +4218,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>110956252</v>
+        <v>110956381</v>
       </c>
       <c r="B36" t="n">
-        <v>89845</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4626,21 +4229,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4651,10 +4254,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>570653.3400563534</v>
+        <v>570686</v>
       </c>
       <c r="R36" t="n">
-        <v>7054866.001286179</v>
+        <v>7054897</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4697,6 +4300,11 @@
       <c r="AB36" t="inlineStr">
         <is>
           <t>21:19</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4723,37 +4331,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>110956330</v>
+        <v>110956508</v>
       </c>
       <c r="B37" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4764,10 +4367,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>570667.8388443358</v>
+        <v>570597</v>
       </c>
       <c r="R37" t="n">
-        <v>7054855.200111266</v>
+        <v>7054867</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4810,6 +4413,11 @@
       <c r="AB37" t="inlineStr">
         <is>
           <t>21:19</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4836,37 +4444,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>110954705</v>
+        <v>110956564</v>
       </c>
       <c r="B38" t="n">
-        <v>89686</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4877,10 +4480,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>570865.1037201436</v>
+        <v>570573</v>
       </c>
       <c r="R38" t="n">
-        <v>7054481.797894709</v>
+        <v>7054885</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4912,7 +4515,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4922,7 +4525,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>21:19</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4949,19 +4557,14 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>110955614</v>
+        <v>110956757</v>
       </c>
       <c r="B39" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4990,10 +4593,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>570772.6988238929</v>
+        <v>570567</v>
       </c>
       <c r="R39" t="n">
-        <v>7054768.543135467</v>
+        <v>7054798</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5025,7 +4628,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5035,12 +4638,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5067,19 +4670,14 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>110954434</v>
+        <v>110956836</v>
       </c>
       <c r="B40" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -5108,10 +4706,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>570809.5760026169</v>
+        <v>570592</v>
       </c>
       <c r="R40" t="n">
-        <v>7054374.194358244</v>
+        <v>7054745</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5143,7 +4741,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5153,7 +4751,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -5185,19 +4783,14 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>110955922</v>
+        <v>110957358</v>
       </c>
       <c r="B41" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -5226,10 +4819,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>570710.3568433803</v>
+        <v>570784</v>
       </c>
       <c r="R41" t="n">
-        <v>7054806.755670385</v>
+        <v>7054448</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5261,7 +4854,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>21:19</t>
+          <t>22:19</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5271,7 +4864,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>21:19</t>
+          <t>22:19</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -5303,15 +4896,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>110955822</v>
+        <v>110955274</v>
       </c>
       <c r="B42" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5319,21 +4907,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5344,10 +4932,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>570735.3624486953</v>
+        <v>570757</v>
       </c>
       <c r="R42" t="n">
-        <v>7054864.270402797</v>
+        <v>7054634</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5377,24 +4965,9 @@
           <t>2023-07-20</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>21:15</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2023-07-20</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>21:15</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5421,15 +4994,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>110955719</v>
+        <v>112074284</v>
       </c>
       <c r="B43" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5437,35 +5005,35 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kulltjärnen, Ång</t>
+          <t>Kulltjärnen, Kulltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>570876.6872800335</v>
+        <v>570619</v>
       </c>
       <c r="R43" t="n">
-        <v>7054840.728085957</v>
+        <v>7054772</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5492,27 +5060,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5527,27 +5090,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>110956299</v>
+        <v>112074385</v>
       </c>
       <c r="B44" t="n">
-        <v>56414</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5555,35 +5113,35 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kulltjärnen, Ång</t>
+          <t>Kulltjärnen, Kulltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>570653.3400563534</v>
+        <v>570621</v>
       </c>
       <c r="R44" t="n">
-        <v>7054866.001286179</v>
+        <v>7054775</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5610,27 +5168,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>21:19</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>21:19</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5645,49 +5198,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>110955757</v>
+        <v>110956299</v>
       </c>
       <c r="B45" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5698,10 +5246,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>570754.6511442953</v>
+        <v>570654</v>
       </c>
       <c r="R45" t="n">
-        <v>7054858.471181084</v>
+        <v>7054866</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5733,7 +5281,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5743,12 +5291,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5775,15 +5323,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>110955639</v>
+        <v>112073661</v>
       </c>
       <c r="B46" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5791,35 +5334,40 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kulltjärnen, Ång</t>
+          <t>Kulltjärnen, Kulltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>570840.3613420491</v>
+        <v>570523</v>
       </c>
       <c r="R46" t="n">
-        <v>7054791.413439409</v>
+        <v>7054775</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5846,22 +5394,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5876,63 +5424,63 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>110955206</v>
+        <v>112073927</v>
       </c>
       <c r="B47" t="n">
-        <v>96265</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kulltjärnen, Ång</t>
+          <t>Kulltjärnen, Kulltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>570765.4646628352</v>
+        <v>570549</v>
       </c>
       <c r="R47" t="n">
-        <v>7054613.522815875</v>
+        <v>7054724</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5959,22 +5507,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5989,67 +5537,58 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>112073635</v>
+        <v>110956446</v>
       </c>
       <c r="B48" t="n">
-        <v>96736</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>6274</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>105336</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kulltjärnen (Kulltjärnen), Ång</t>
+          <t>Kulltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>570513</v>
+        <v>570628</v>
       </c>
       <c r="R48" t="n">
-        <v>7054747</v>
+        <v>7054923</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6076,22 +5615,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-07-20</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-07-20</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6106,63 +5645,58 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>112074315</v>
+        <v>110955206</v>
       </c>
       <c r="B49" t="n">
-        <v>96736</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kulltjärnen (Kulltjärnen), Ång</t>
+          <t>Kulltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>570621</v>
+        <v>570765</v>
       </c>
       <c r="R49" t="n">
-        <v>7054778</v>
+        <v>7054614</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6189,22 +5723,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>18:44</t>
+          <t>2023-07-20</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>18:44</t>
+          <t>2023-07-20</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6219,27 +5743,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>112073748</v>
+        <v>110490944</v>
       </c>
       <c r="B50" t="n">
-        <v>96736</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6264,22 +5783,18 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kulltjärnen (Kulltjärnen), Ång</t>
+          <t>Kulltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>570532</v>
+        <v>570655</v>
       </c>
       <c r="R50" t="n">
-        <v>7054761</v>
+        <v>7054696</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6306,22 +5821,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>18:09</t>
+          <t>2023-06-30</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>18:09</t>
+          <t>2023-06-30</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>50-tal plantor</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6336,68 +5846,65 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>112073927</v>
+        <v>110542945</v>
       </c>
       <c r="B51" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kulltjärnen (Kulltjärnen), Ång</t>
+          <t>Kulltjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>570548</v>
+        <v>570493</v>
       </c>
       <c r="R51" t="n">
-        <v>7054724</v>
+        <v>7054671</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6424,22 +5931,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>18:19</t>
+          <t>2023-07-01</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>18:19</t>
+          <t>2023-07-01</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6448,74 +5945,72 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>112073661</v>
+        <v>110542946</v>
       </c>
       <c r="B52" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kulltjärnen (Kulltjärnen), Ång</t>
+          <t>Kulltjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>570523</v>
+        <v>570492</v>
       </c>
       <c r="R52" t="n">
-        <v>7054775</v>
+        <v>7054680</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6542,22 +6037,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>18:03</t>
+          <t>2023-07-01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>18:03</t>
+          <t>2023-07-01</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6566,33 +6051,29 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>112074007</v>
+        <v>110957165</v>
       </c>
       <c r="B53" t="n">
-        <v>96736</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6617,22 +6098,18 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kulltjärnen (Kulltjärnen), Ång</t>
+          <t>Kulltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>570552</v>
+        <v>570689</v>
       </c>
       <c r="R53" t="n">
-        <v>7054717</v>
+        <v>7054561</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6659,22 +6136,27 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-07-20</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>22:19</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-07-20</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>22:19</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>60-tal plantor</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6689,27 +6171,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>112074220</v>
+        <v>110957182</v>
       </c>
       <c r="B54" t="n">
-        <v>96736</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6734,22 +6211,18 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kulltjärnen (Kulltjärnen), Ång</t>
+          <t>Kulltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>570573</v>
+        <v>570715</v>
       </c>
       <c r="R54" t="n">
-        <v>7054742</v>
+        <v>7054561</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6776,22 +6249,27 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-07-20</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>22:19</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-07-20</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>22:19</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>60-tal plantor</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6806,27 +6284,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>112074850</v>
+        <v>112073383</v>
       </c>
       <c r="B55" t="n">
-        <v>96736</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6853,20 +6326,20 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>200</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kulltjärnen (Kulltjärnen), Ång</t>
+          <t>Kulltjärnen, Kulltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>570507</v>
+        <v>570562</v>
       </c>
       <c r="R55" t="n">
-        <v>7054761</v>
+        <v>7054716</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6898,7 +6371,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6908,7 +6381,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6935,51 +6408,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>112074385</v>
+        <v>112073564</v>
       </c>
       <c r="B56" t="n">
-        <v>78714</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Kulltjärnen (Kulltjärnen), Ång</t>
+          <t>Kulltjärnen, Kulltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>570621</v>
+        <v>570581</v>
       </c>
       <c r="R56" t="n">
-        <v>7054776</v>
+        <v>7054735</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -7011,7 +6483,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7021,7 +6493,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7048,15 +6520,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>112074371</v>
+        <v>112073635</v>
       </c>
       <c r="B57" t="n">
-        <v>96736</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7083,20 +6550,20 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kulltjärnen (Kulltjärnen), Ång</t>
+          <t>Kulltjärnen, Kulltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>570623</v>
+        <v>570513</v>
       </c>
       <c r="R57" t="n">
-        <v>7054780</v>
+        <v>7054748</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -7128,7 +6595,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7138,7 +6605,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7168,12 +6635,7 @@
         <v>112073706</v>
       </c>
       <c r="B58" t="n">
-        <v>96736</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7206,14 +6668,14 @@
       <c r="K58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kulltjärnen (Kulltjärnen), Ång</t>
+          <t>Kulltjärnen, Kulltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
         <v>570517</v>
       </c>
       <c r="R58" t="n">
-        <v>7054754</v>
+        <v>7054755</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7282,51 +6744,50 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>112074284</v>
+        <v>112073748</v>
       </c>
       <c r="B59" t="n">
-        <v>78714</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Kulltjärnen (Kulltjärnen), Ång</t>
+          <t>Kulltjärnen, Kulltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>570619</v>
+        <v>570532</v>
       </c>
       <c r="R59" t="n">
-        <v>7054772</v>
+        <v>7054761</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7358,7 +6819,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7368,7 +6829,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7395,15 +6856,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>112073564</v>
+        <v>112074007</v>
       </c>
       <c r="B60" t="n">
-        <v>96736</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7430,20 +6886,20 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kulltjärnen (Kulltjärnen), Ång</t>
+          <t>Kulltjärnen, Kulltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>570581</v>
+        <v>570552</v>
       </c>
       <c r="R60" t="n">
-        <v>7054735</v>
+        <v>7054717</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7475,7 +6931,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7485,7 +6941,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7512,15 +6968,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>112073383</v>
+        <v>112074184</v>
       </c>
       <c r="B61" t="n">
-        <v>96736</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7547,20 +6998,20 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>70</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kulltjärnen (Kulltjärnen), Ång</t>
+          <t>Kulltjärnen, Kulltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>570562</v>
+        <v>570578</v>
       </c>
       <c r="R61" t="n">
-        <v>7054716</v>
+        <v>7054744</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7592,7 +7043,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7602,7 +7053,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7629,15 +7080,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>112074829</v>
+        <v>112074220</v>
       </c>
       <c r="B62" t="n">
-        <v>96736</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7664,20 +7110,20 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kulltjärnen (Kulltjärnen), Ång</t>
+          <t>Kulltjärnen, Kulltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>570501</v>
+        <v>570573</v>
       </c>
       <c r="R62" t="n">
-        <v>7054758</v>
+        <v>7054742</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7709,7 +7155,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7719,7 +7165,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7749,12 +7195,7 @@
         <v>112074296</v>
       </c>
       <c r="B63" t="n">
-        <v>96736</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7787,11 +7228,11 @@
       <c r="K63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Kulltjärnen (Kulltjärnen), Ång</t>
+          <t>Kulltjärnen, Kulltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>570620</v>
+        <v>570619</v>
       </c>
       <c r="R63" t="n">
         <v>7054773</v>
@@ -7863,15 +7304,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>112074184</v>
+        <v>112074315</v>
       </c>
       <c r="B64" t="n">
-        <v>96736</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7896,22 +7332,18 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kulltjärnen (Kulltjärnen), Ång</t>
+          <t>Kulltjärnen, Kulltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>570578</v>
+        <v>570621</v>
       </c>
       <c r="R64" t="n">
-        <v>7054744</v>
+        <v>7054777</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7943,7 +7375,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7953,7 +7385,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7977,6 +7409,440 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>112074371</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Kulltjärnen, Kulltjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>570623</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7054780</v>
+      </c>
+      <c r="S65" t="n">
+        <v>25</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>112074829</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Kulltjärnen, Kulltjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>570501</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7054758</v>
+      </c>
+      <c r="S66" t="n">
+        <v>25</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>112074850</v>
+      </c>
+      <c r="B67" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Kulltjärnen, Kulltjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>570507</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7054761</v>
+      </c>
+      <c r="S67" t="n">
+        <v>25</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>110490866</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Kulltjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>570673</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7054685</v>
+      </c>
+      <c r="S68" t="n">
+        <v>25</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2023-06-30</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2023-06-30</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28663-2023 artfynd.xlsx
+++ b/artfynd/A 28663-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY68"/>
+  <dimension ref="A1:AZ68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110490783</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110954705</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110956010</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110956165</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110490772</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110542947</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1384,6 +1419,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110542948</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1492,6 +1532,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110956330</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1600,6 +1645,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110957421</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1708,6 +1758,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110955882</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1816,6 +1871,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110955973</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1924,6 +1984,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110956252</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2022,6 +2087,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110955652</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2120,6 +2190,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110954865</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2228,6 +2303,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110956168</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2326,6 +2406,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110490872</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2429,6 +2514,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110954395</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2532,6 +2622,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110954434</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2635,6 +2730,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110954677</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2738,6 +2838,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110954981</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2841,6 +2946,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110955090</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2944,6 +3054,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110955216</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3047,6 +3162,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110955319</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3150,6 +3270,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110955501</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3253,6 +3378,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110955580</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3356,6 +3486,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110955614</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3454,6 +3589,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110955639</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3557,6 +3697,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110955691</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3660,6 +3805,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110955719</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3763,6 +3913,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110955757</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3876,6 +4031,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110955822</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3989,6 +4149,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110955922</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4102,6 +4267,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110956103</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4215,6 +4385,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110956348</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4328,6 +4503,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110956381</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4441,6 +4621,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110956508</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4554,6 +4739,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110956564</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4667,6 +4857,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110956757</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4780,6 +4975,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110956836</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4893,6 +5093,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110957358</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4991,6 +5196,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110955274</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5099,6 +5309,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112074284</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5207,6 +5422,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112074385</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5320,6 +5540,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110956299</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5433,6 +5658,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112073661</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5546,6 +5776,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112073927</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5654,6 +5889,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110956446</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5752,6 +5992,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110955206</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5855,6 +6100,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110490944</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5961,6 +6211,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110542945</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6067,6 +6322,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110542946</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6180,6 +6440,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110957165</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6293,6 +6558,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110957182</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6405,6 +6675,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112073383</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6517,6 +6792,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112073564</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6629,6 +6909,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112073635</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6741,6 +7026,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112073706</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6853,6 +7143,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112073748</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6965,6 +7260,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112074007</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7077,6 +7377,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112074184</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7189,6 +7494,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112074220</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7301,6 +7611,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112074296</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7409,6 +7724,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112074315</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7521,6 +7841,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112074371</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7633,6 +7958,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112074829</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7745,6 +8075,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112074850</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7843,8 +8178,82 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110490866</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>